--- a/src/test/resources/input/AI_Test_Data.xlsx
+++ b/src/test/resources/input/AI_Test_Data.xlsx
@@ -3,23 +3,19 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\Nagireddy\Selenium\ai-response-validation-framework\src\test\resources\input\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7650"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14370" windowHeight="6135"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
+  <oleSize ref="A1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
     <t>Query</t>
   </si>
@@ -28,42 +24,6 @@
   </si>
   <si>
     <t>Actual_Response</t>
-  </si>
-  <si>
-    <t>How can I enroll a learner in my course on the LMS?</t>
-  </si>
-  <si>
-    <t>" Enrolling a learner in a course Option 1: Learner self-enrollment Learners can enroll themselves in a course directly from the learning interface: Log in to the learning account. From the home or “Recommended Courses” area, select Search or Browse Catalog. Locate the desired course and click the course card. On the course information page, click Enroll (or Pay &amp; Enroll if it is a paid course). After this, the learner is enrolled and the course appears on their learning list or transcript. Option 2: Allowing or restricting self-registration (for ILT/VILT events) When you create a classroom or virtual course event, you can control whether learners can enroll themselves or must be added by an admin: During course event setup, in the Self-Registration section, choose: Yes, learners can register themselves for this course event – learners enroll directly from the catalog/event listing. No, learners will be manually assigned by an admin or training manager – only admins/managers can add learners to the roster. Optionally configure: Registration Approval (Yes/No) if you want manager/admin approval for enrollments. Waiting List and capacity (minimum/maximum learners) to control how many can enroll and how waitlists are handled. Complete the scheduling and Submit the event so it appears for learners to enroll (if self-registration is enabled). Option 3: Admin/manager enrollment into ILT sessions For instructor-led (classroom or virtual) sessions, admins or instructors can enroll learners directly into a session roster instead of relying on self-registration. This is typically done from the session/event management area or via tools like the registrar/roster or Learning Assignment Tool, depending on your configuration. Sources: Learning Experience: How do I Enroll/Un-Enroll for a Course? - Steps for learner self-enrollment in a course Creating Classroom Course Events (ILT) – Self-Registration and Scheduling - Options for self-registration, approval, waitlists, and publishing events for enrollment Learning catalog and registrar concepts - Describes classes, catalog, and registrar for managing enrollments "</t>
-  </si>
-  <si>
-    <t>"Enrolling a learner in a course on the LMS You can enroll learners in a course in two main ways: self-enrollment by the learner, or admin-driven enrollment. The exact options depend on how the course and your portal are configured. 1. Let learners self-enroll For self-enrollment to work, the course must allow self-registration: When creating or editing a self-paced course, set Self-registration to: Yes, learners can register themselves for this course. Optionally, configure: LXP Channels / Groups where the course appears. Privacy as Public (any learner can find it) or Private (restricted to selected users/groups). Publish the course so it appears in the catalog/LXP. Once that is set, learners can enroll themselves: Log in to the LMS/LXP. Use Search or Browse Catalog / Learner Home to find the course. Open the course card/info page. Click Enroll (or Pay &amp; Enroll if it is a paid course). 2. Enroll learners as an administrator If you want to control enrollment yourself (for ILT sessions or online courses): Ensure the learner is an active user (inactive users cannot be enrolled directly into ILT sessions). Use the Learning Assignment Tool (LAT) to assign: Select the course or ILT session. Define the target population (specific users, groups, or criteria). Process the assignment so the course appears on their transcript / Learner Home. For ILT sessions, you can also: Moderate enrollments based on class capacity. Enroll learners directly into a specific session from the ILT administration area. 3. Special notes If a user is inactive but must appear historically in an ILT session, you must temporarily activate them, enroll via LAT, then deactivate again. For embedded/learning-experience setups, once a course (or credential) is created and assigned, it appears in the LMS catalog on the LXP, and learners can launch and complete it from there. Sources: Learning Experience: How do I Enroll/Un-Enroll for a Course? - Steps for learner self-enrollment and unenrollment. Self-paced course setup and self-registration options - How to enable learner self-registration, set channels/groups, and privacy. Enrolling inactive users to ILT sessions - Limitation on inactive users and workaround using activation and LAT. Embedded LMS overview - How courses, offers, credentials, and catalog assignment work in the embedded LMS/LXP model. ILT and vILT administration overview - Admin responsibilities for ILT/vILT events and sessions."</t>
-  </si>
-  <si>
-    <t>How do I create and assign a quiz or assessment in the LMS?</t>
-  </si>
-  <si>
-    <t>" Create and Assign a Quiz or Assessment in the LMS 1. Create a Learning Assessment (Cornerstone Learning) Open Assessments Home Go to Admin &gt; Tools &gt; Learning &gt; Catalog Management and select Learning Assessments BETA. Click Create Assessment to start a new assessment. Enter Assessment Details Provide an Assessment Title, Description, and Instructions. Optionally add Internal Notes for admins. Choose how it is scored: Yes, require 80%+ score to pass – users must score at least 80% to pass. No, disable scoring – no pass/fail score is required. Select the Assessment Format: Show multiple questions on pages – questions grouped by section, each section on a new page. Show one question at a time – one question per page. Build the Assessment Structure (Assessment Builder) On the Assessment Builder step, configure sections and questions. Add sections: Click Add Title, enter a Section Title (up to 500 characters) and optional Section Description (up to 1000 characters), then Save. Add more sections via Add Section or the hover menu between sections. Add questions: Within a section, click Add Question. Enter the question text. Configure answer choices: Two choices are added by default; add more with Add Choice. Use Mark if Correct to indicate the correct answer (only one choice can be marked correct). Edit Answer Text, reorder with Move Up/Move Down, or remove with the X icon. Click Save to add the question to the assessment. Reorganize content: Move sections or questions up/down using the arrows. Edit or delete sections and questions as needed. Save and Publish Click Save to store the assessment as a Draft on the Assessments Home page. When ready, open the assessment from Assessments Home and click Publish. Confirm in the pop-up by selecting Yes, publish. Important: You must have at least one question; otherwise publishing will fail. After publishing: The assessment appears in the Assessments table with status Published and can be Launched for preview. Published assessments become available in the Course Console and can be selected in the Learning Assignment Tool. 2. Create Questions in the Question Bank (Optional but Recommended) You can prebuild reusable questions in the Question Bank and then add them to multiple assessments. Open Question Bank From Assessments Home, click the Question Bank tab. Create a Question Click Create Question. Enter the Question text. Add answer choices: Use Mark if Correct to identify correct answers. Enter Answer Text, reorder with arrows, and delete with the trash icon. For Text Only questions, you can choose to ignore case when evaluating answers. Select a Category to organize the question. Optionally add an Explanation that learners can see when reviewing their assessment. Ensure the question is marked Active if you want it available for use. 3. Assign the Assessment to Learners Once the assessment is published, you can assign it to users’ transcripts using the Learning Assignment Tool (LAT). Open the Learning Assignment Tool Go to Admin &gt; Tools &gt; Learning and click Assignment Tool. On the Manage Learning Assignments page, click Create Assignment. Select the Assessment as Training On the Setup step, search for training and select the Assessment learning object. Use the Assessment training type filter if needed to find it quickly. Configure Assignment Options Only Standard (one-time) assignments are supported for assessments; dynamic assignments are not yet supported. When assigning assessments: Status options are limited to Assigned, Approved, and Registered. Due date options are disabled. Email options cannot be configured. You cannot set a new occurrence for the assignment. Complete the remaining assignment steps (users, schedule, etc.) as appropriate and submit the assignment. Result Selected users receive the assessment on their transcripts and can launch it from the web or the Learn app. 4. Alternative: Use a Test Learning Object and Curriculum (Classic Test Engine) If you are using the classic Test Engine instead of Learning Assessments, you can: Create Test Questions and Test Create questions in the Question Bank (Test Engine). Create a Test learning object and add those questions. Attach the Test to a Course via a Curriculum Create a Curriculum that includes both the course and the test. Set the curriculum so the course must be completed before the test, or allow the test to be taken independently. Assign the Curriculum Assign the curriculum using the Learning Assignment Tool so users complete the course and then the test. 5. Creating Quizzes Inside Courses (Authoring Tool Quizzes) If you are building content with the in-platform Create Tool, you can embed quizzes directly in a course: Add a Quiz to a Course Create or open a course in the Create tool. Select one of the available quiz cards (e.g., ranking or matching quizzes). Add prompts and responses, define the correct order or matches, and save. Deliver the Course Publish the course and assign it like any other online course; the embedded quiz provides in-course knowledge checks. Sources: Create Assessments &amp; Assessment Builder - How to create assessment details, configure sections and questions, save drafts, and publish assessments. Assessments Home - Accessing Assessments Home, managing drafts and published assessments. Learning Assessments - Question Bank - Creating and managing reusable questions in the Question Bank. Learning Assessments (OpenBeta) - Learning Assignment Tool - Assigning assessments via the Learning Assignment Tool and related limitations. How do I assign or attach a test to a Learning Object? - Bundling tests with courses using curricula to ensure users take a test. Create Tool - Quizzes - Adding ranking and matching quizzes inside authored courses. "</t>
-  </si>
-  <si>
-    <t>"Creating and Assigning a Quiz or Assessment in the LMS 1. Create a Learning Assessment (new Assessment tool) Open Assessments Home Go to Admin &gt; Tools &gt; Learning &gt; Catalog Management and click Learning Assessments BETA. On the Assessments Home page, click Create Assessment. Enter Assessment Details On the Assessment Details step: Set an Assessment Title, Description, and Instructions. Add any Internal Notes for admins. Choose how it is scored (e.g., require 80%+ to pass or disable scoring). Select the Assessment Format: Show multiple questions on pages (questions grouped by section, each section is a page), or Show one question at a time. Build the Assessment Structure In the Assessment Builder: Add and configure sections (title and description). Within each section, click Add Question: Enter the question text. Add answer choices (at least two by default). Mark which choice is correct (only one can be marked correct). Use Move Up/Down arrows to reorder choices or questions. Use X to delete choices or questions. Use section-level options to move, edit, or delete sections. Save and Publish Click Save to keep the assessment as a Draft (manageable from Assessments Home). When ready, click Publish: Confirm in the pop-up (Yes, publish). You must have at least one question; otherwise publishing will fail. After publishing, the assessment appears on Assessments Home in Published status and can be launched or assigned. Published assessments are locked from further editing (no in-place versioning). 2. (Optional) Reuse Questions via Question Bank If you want reusable questions, use the Learning Assessments Question Bank: From Learning Assessments BETA, click the Question Bank tab. Click Create Question to add questions with a type (e.g., multiple choice, true/false) and category. These questions can then be pulled into multiple assessments. 3. Assign the Assessment to Learners (Learning Assignment Tool) Open the Learning Assignment Tool (LAT) Go to Admin &gt; Tools &gt; Learning &gt; Assignment Tool and click Create Assignment. Select the Assessment as Training In the Setup / Select Training step: Search for the published assessment. Filter by the Assessment training type if needed. Select the assessment as the learning object to assign. Configure the Assignment Only Standard learning assignments are supported for assessments (no dynamic assignments). Status options are limited to Assigned, Approved, and Registered. Due dates, new occurrence, and recurring options are not available when an assessment is included. If you include other training types in the same assignment (e.g., curriculum, material), these limitations apply to them as well. Select Users and Submit Choose the target users or OUs, finalize the configuration, and submit the assignment. The assessment will appear on users’ transcripts for launch. 4. Alternative: Classic Test Engine “Test” Learning Objects If you are using the classic Test Engine instead of Learning Assessments, the flow is: Create questions in the Question Bank (with categories). Create a Test learning object: Set test details (name, attempts allowed, score visibility, etc.). Configure sections and add questions from the question bank, with options for randomization and custom weighting. Deliver the test: Use it as a stand-alone learning object, or Add it into a Curriculum with other learning objects (e.g., course + test) so learners must complete the course then the test. Assign the test via: A curriculum (recommended for course + test flows), or The Learning Assignment Tool or Learning Details page (assigning the test LO directly). 5. Quick Option: Simple Quiz SmartCards (LXP / Pathway) In the LXP/Pathway experience, you can also create a simple Quiz SmartCard: Create a Pathway and add a Quiz card. Define the question and correct answer; optionally allow multiple attempts. Use Leaps and Locks to control navigation and access to other SmartCards based on quiz completion. Sources: Create Assessments &amp; Assessment Builder - How to create, structure, save, and publish assessments. Assessments Home - Accessing and managing assessments. Learning Assessments - Learning Assignment Tool - Assigning assessments via standard learning assignments and related limitations. Learning Assessments - Question Bank - Creating reusable questions for assessments. How do I assign training to users? - General methods for assigning training via Learning Assignment Tool or Learning Details. Publish Assessment &amp; Availability - Publishing assessments and making them available for assignment. Learning Assessments - Admin Experience (Open Beta) - Overview of Learning Assessments capabilities and exclusions. Create Tool - Quizzes - Creating ranking and matching quizzes for interactive knowledge checks."</t>
-  </si>
-  <si>
-    <t>Where can I track learner progress and completion reports?</t>
-  </si>
-  <si>
-    <t>" Tracking learner progress and completion in the LMS 1. Individual learner progress and completions User Transcript: Go to Admin &gt; Tools &gt; Core Functions &gt; Users, search for the user, and click View Transcript. From there you can: See Active (incomplete) training Switch the Training Status filter to Completed to see all completions Open View Training Details for assignment dates, registration dates, completion dates, version history, and transcript history Your Transcript widget / Learner Home: Learners can see their own progress via the Your Transcript widget and other widgets such as My Training, Required Training, and Online Training in Progress, which surface assigned, in-progress, and required items. Cohort Learning tab: In cohort communities, the Learning tab lets enrolled users view and track progress on all learning objects required for that cohort, and access the Training Completion page once all required LOs are finished. 2. Manager / admin reports for progress and completion Training Progress Summary Pie Chart Report (Standard Report): Recommended as the primary report to see usage and status of active learning objects. It shows the distribution of statuses (e.g., Not Started, In Progress, Completed) and can be used as a dashboard view of course-level progress. Training Progress Pie Chart (Recommended for Managers): Lets managers see the progress of their direct and indirect reports on specific or multiple learning objects and drill into particular statuses directly from the dashboard. Training Status Summary (Recommended for Managers): Summarizes where each user stands (e.g., who is overloaded, who is on track) across their assigned learning. Transcripts report (Track Employees): Gives managers access to their team’s transcripts so they can monitor learning activities and completions. SCORM 2004 Course Progress Chart Report: Provides a pie chart and detailed table with course status, pass/fail, score, time spent, attempts, and last accessed date for online courses, plus training object ID and title in the Excel export. Online Training Status / Online Course Attempts Reports: These standard training reports show transcript status, progress, registration number, and score for online courses, including recurring training. Card completion in live event reports (Learning Experience): Live event reports now include card completion status, linking registration data with completion records so admins can see who actually completed live event content. Assignment performance &amp; LXP reports: In Learning Experience, pre-built reports and dashboards (user, content, assignment, channel, and group reports) show: Assignment status (Not Started / Started / Completed) Content completions, likes, comments Channel and group engagement, including completion tracking for assignments associated with groups 3. Reporting 2.0 – progress-specific fields Maintain Progress / Progress Maintained fields in Reporting 2.0: Progress Maintained? (Assignment section) – shows Yes/No if the Maintain Progress option was enabled on the learning assignment. Progress Maintained (Transcript section) – indicates whether a user’s assignment used the Maintain Progress option. These fields help you understand how progress is handled when users are re-assigned or versioned into new instances of training. 4. Where to start, depending on your role As an admin: Use User Transcript for single-learner investigations and standard reports like Training Progress Summary Pie Chart, Online Training Status, and SCORM 2004 Course Progress Chart for course-level progress and completion. As a manager: Use recommended Track Employee reports: Training Progress Pie Chart, Training Status Summary, and Transcripts to monitor your team’s completion and progress. In Learning Experience (LXP): Use the built-in assignment, content, channel, group, and live event reports to track card-level completions and engagement. Sources: User transcript and training details - How to open a user’s transcript and view assignment, registration, completion, and progress details. Learner Home widgets - Widgets such as Your Transcript, My Training, Required Training, and Online Training in Progress for tracking learner progress. Learning Object Usage / Training Progress Summary Pie Chart - Recommended standard report for active learning objects and usage. Recommended Standard Reports for Managers - Lists Training Progress Pie Chart, Training Status Summary, and Transcripts as key Track Employee reports. SCORM 2004 Course Progress Chart Report - Output fields for course status, completion, score, time spent, and attempts. Card completion status in live event reports - Live event reports enhanced to show card completion status and detailed learner progress. Learning Experience reporting - Pre-built LXP reports for user, content, assignments, channels, and groups with progress and completion tracking. Reporting – Progress Maintained - New Reporting 2.0 fields to see whether progress is maintained on assignments and transcripts. Cohort Community – Learning - Cohort Learning tab and Training Completion page for tracking cohort-required learning. "</t>
-  </si>
-  <si>
-    <t>"Tracking learner progress and completion in the LMS 1. Individual learner progress and completions User Transcript Go to Admin &gt; Tools &gt; Core Functions &gt; Users, search for the learner, and click View Transcript. From there you can: See Active, Completed, Archived, and Removed training. Use Search by Keyword to find a specific course. Open View Training Details to see assignment date, registration date, completion date, version history, and transcript history, plus the overall completion status. Transcript Details page (per training) From the transcript, open the training’s details to: Review assignment/version history and audit trail. Check or adjust status (e.g., In Progress, Completed, Exempt) and dates when needed. Use it as a “control panel” for troubleshooting completion issues and providing audit evidence. 2. Cohort / program progress Cohort Community – Learning tab Learners enrolled in a cohort can open Connect &gt; All Communities &gt; [Cohort] &gt; Learning to: See overall cohort progress as a percentage. Track completion of required learning objects within the cohort. View completion page and training details for the cohort when enabled. Cohort completion behavior Cohorts show incremental progress as LOs are completed, but the cohort status only changes to Completed on the cohort end date, even if all required items are finished earlier. 3. Manager / admin reports for progress and completion Training Progress Pie Chart Report Path: Reports &gt; Standard Reports &gt; Track Employees &gt; Training Progress Pie Chart. Use this to: See a pie chart of transcript statuses (Registered/Not Started, In Progress, Completed, etc.) for a specific learning object. Drill into a slice to view which users are in each status. Curriculum Report Path: Reports &gt; Standard Reports &gt; Training &gt; Curriculum. This shows detailed transcript status and % Met for users in a curriculum (program), at summary or detailed level. SCORM 2004 Course Progress Chart Report Path: Reports &gt; Standard Reports &gt; Training &gt; SCORM 2004 Course Progress Chart. Provides: Course-level progress and status distribution (Registered, In Progress, Completed, etc.). Module-level completion, pass/fail, scores, time spent, and attempts. Single-user module status when you need granular tracking. Course Assessment Results Shows course status, completion date, overall score, and SCO/module status and scores for online courses, including recurring instances. Reporting 2.0 – Assignment / Transcript reports In Reports &gt; Reporting 2.0, you can build: Custom assignment reports (e.g., to see Maintain Progress settings and assignment status). Custom transcript reports to track user-level completion history across trainings. 4. Learning Experience (LXP) progress and engagement LXP pre-built reports In Learning Experience, administrators can use: User reports – what each user has created, completed, viewed, commented on, or bookmarked. Content reports – completions, likes, comments, and popularity of content. Assignment reports – status of assigned content (Not Started, Started, Completed). Channel and group reports – engagement with channels and groups, including visits, unique visitors, and content interactions. Live event reports (LXP) Live event reports now include card completion status, so you can see both registration and actual completion for live event cards. 5. Integration-specific completion tracking LinkedIn Learning, edX, Coursera, LTI, etc. For integrated providers: Completions are automatically recorded on the LMS transcript when learners finish the external course. Progress and completion can then be reported using the same LMS reports (transcript, standard reports, Reporting 2.0). LMS ↔ LXP completion flow For SmartCards and LXP content linked to LMS: Completion flows from LMS to LXP, not the other way around. Learners must launch and complete the content in the LMS; then the completion syncs back and marks the LXP card complete. Sources: Viewing learner transcripts and training details - How to open a user’s transcript, locate specific training, and view detailed assignment/completion history. Cohort Community - Learning - Tracking cohort learning objects and overall cohort progress from the Learning tab. Cohort Community - Progress Display - How cohort progress and completion status are calculated and when cohorts move to Completed. Training Progress Pie Chart Report - Manager report showing status distribution for a specific training and drill-down to user lists. Curriculum Report - Report for curriculum-level user progress and % Met. SCORM 2004 Course Progress Chart Report - Course and module progress, status, scores, and time spent for SCORM 2004 courses. Learning Experience reporting - LXP reports for users, content, assignments, channels, and groups. Card completion status in live event reports - How live event reports now include completion status for event cards. Reporting 2.0 - Progress Maintained - Reporting 2.0 capabilities and assignment/transcript custom reports. SmartCard completions and LMS/LXP flow - Explanation that completions flow from LMS to LXP and must be completed in LMS to reflect in LXP."</t>
-  </si>
-  <si>
-    <t>Can I bulk upload students and manage their roles?</t>
-  </si>
-  <si>
-    <t>" Bulk uploading students and managing their roles 1. Bulk upload / creation of users (students) You can bulk upload or create users in multiple ways: LXP Admin CSV upload: Navigate to Admin &gt; Accounts &gt; Users &gt; Add Users, use the Multiple Users Upload tab, download the sample CSV, populate required fields (e.g., first_name, last_name, email, optional groups, etc.), then upload the CSV to create many users at once. LXP Bulk Import / Update: The same CSV mechanism can be used to add many users or update their information in one operation, including custom fields and community (group) membership. Edge Import (LMS): For large-scale user management in the LMS, you can use Edge Import with the Employee (CHR) template to create or update user accounts in bulk. 2. Managing roles in bulk Roles can be managed in bulk within the LXP: Bulk update roles via CSV (LXP): Use Admin &gt; Learning experience (legacy) &gt; Accounts &gt; Users (or Admin &gt; System settings &gt; People &amp; organization &gt; People &gt; Users) and click Bulk Update. In the sample CSV, you can: Specify the user by email (required). Use add_roles to assign roles (e.g., member, admin, group_leader, group_admin, sme, etc.). Use remove_roles to remove roles from users. Only users listed in the file are updated; users not listed are not deleted. Bulk role updates are only via the bulk update sheet: For LXP roles, using this bulk update CSV is explicitly noted as the only supported way to make bulk role changes. Per-user role assignment (UI): You can also assign roles individually by going to Admin &gt; Accounts &gt; Users, locating a user, clicking Role, and updating their roles (e.g., Member, Admin, Collaborator, Curator, SME, Group Admin, Group Leader, etc.). 3. Bulk adding users to communities / groups If you also need to manage group/community membership for students: In the LXP user CSV, you can populate the groups field with community titles to add users to those communities during bulk upload. Group Creators, Group Admins, or Group Leaders can use a Bulk Upload option within a community to add multiple existing users to that community at once (typically via a template with user IDs or emails). There is also a specific flag that allows bulk upload of community members, enabling Group Admins/Leaders to add up to a defined limit of users directly into a community without invitation acceptance. 4. Summary Yes, you can: Bulk upload students into both the LXP and LMS (via CSV in LXP and via Edge Import in LMS). Manage their roles in bulk using the LXP bulk update CSV (add/remove roles) and individually via the Admin UI. Optionally bulk manage their community/group membership as part of the same processes. Sources: Bulk import users using a CSV file - Describes downloading and populating the LXP sample CSV for bulk user creation and supported fields (including groups). Update user information in bulk - Explains bulk update CSV for status and roles (add_roles, remove_roles) and how to upload it. Making bulk update to roles in the LXP - Confirms bulk update sheet is the only way to bulk update roles and that unlisted users are not deleted. Role Based Access Control in LXP - Details standard roles and per-user role assignment via Admin &gt; Accounts &gt; Users &gt; Role. How can I Upload or Update Users in Bulk? (Edge Import) - Describes using Edge Import Employee (CHR) template to bulk create/update LMS users. Bulk add users to a Community (Group) in LXP - Explains bulk upload of users into communities/groups by Group Admin/Leader. Directly Adding Users to Communities Without Invitation Acceptance - Describes enabling bulk upload of community members and limits for direct addition. "</t>
-  </si>
-  <si>
-    <t>"Bulk uploading students and managing their roles 1. Bulk upload / creation of users (students) You can bulk upload users into the system in several ways, depending on volume and whether you are using the LMS or the Learning Experience (LXP) module: LXP / Learning Experience – Admin UI CSV upload Go to Admin &gt; Learning experience (legacy) &gt; Accounts &gt; Users or Admin &gt; System settings &gt; People &amp; organization &gt; People &gt; Users. Click Add Users, then the Multiple Users Upload tab. Download Sample file to get the correct CSV format. The sample file requires at least: first_name, last_name (recommended) email (required, must be unique) Optional fields like password, groups, picture_url, custom fields, etc. Save as CSV UTF‑8 and upload it via Multiple Users Upload &gt; Upload CSV File, then Preview and Import. Duplicate emails are ignored or can cause conflicts, so each email must be unique. LXP – Bulk update of existing users Use Bulk Update from the same Users page to change status and roles in bulk. Download the Bulk Update sample CSV, which includes: email (required identifier) status (e.g., active, deleted, suspended) add_roles and remove_roles (e.g., admin, member, manager, group_leader, group_admin, sme, etc.). Upload the CSV via Bulk Update &gt; Select CSV File, then Preview and Import. LMS / Enterprise scale – Edge Import For large volumes, use Edge Import with the Employee (CHR) template to create or update user accounts in bulk. Edge Import supports: Manual loads and scheduled feeds Primary keys like User ID and GUID It is recommended to test loads in a Pilot/Stage environment before Production. 2. Managing roles effectively (assignment and bulk changes) Role concepts in Learning Experience LXP provides standard roles such as Member, Admin, Curator, Collaborator, SME, and targeted roles like Group Admin, Group Leader, and Trusted Collaborator. You can also create custom roles. Create and configure roles Navigate to Admin &gt; Learning experience (legacy) &gt; Accounts &gt; Roles or Admin &gt; System settings &gt; People &amp; organization &gt; People &gt; Security roles. Click Add New Role, name the role, select the permissions, and Save. You can later add or remove permissions from roles via the same Roles page. Assign roles to users individually Go to Admin &gt; … &gt; Users. Locate the user and click Role. Select one or more roles in the Select roles dropdown and Save. Every user automatically has the Member role; this cannot be removed. Assign roles in bulk (recommended for many students) Use the Bulk Update CSV: Include email plus add_roles and/or remove_roles. Populate add_roles with the role names you want to grant (e.g., member, manager, group_leader). Upload via Bulk Update to apply role changes to all listed users at once. Alternatively, when doing a Multiple Users Upload for new users, you can include a role column (for LXP bulk upload) to assign roles as part of creation. Community / Group-related roles and membership You cannot assign a role directly to a community itself; roles are assigned to users. To manage community membership in bulk: Use the Bulk Upload option from within a group (community) if you are a Group Creator, Group Admin, or Group Leader. Download the sample template, populate user identifiers (e.g., email), and upload to add members in bulk. With the Bulk Upload of Community Members flag enabled, Group Admins/Leaders can add up to 500 users at a time directly into a community without invitation acceptance. 3. Practical approach for your use case Decide the primary tool: Use Multiple Users Upload / Bulk Update for moderate volumes and LXP-focused scenarios. Use Edge Import (Employee) for very large, recurring loads from HR or SIS systems. Prepare a standard CSV template including: User identifiers (email, first/last name, external_id if needed) Any required custom fields Role columns (add_roles) for role assignment. Load users first, validate that they appear correctly. Run a Bulk Update to: Activate users (status = active) Assign appropriate roles (e.g., student/member, manager, group_leader). Optionally bulk add them to communities/groups using the group Bulk Upload feature if you organize students by communities. Sources: Bulk import users using a CSV file (Multiple Users Upload) - Describes downloading the sample CSV, required fields, and uploading many users at once. Update user information in bulk (Bulk Update) - Explains bulk updating user status and roles via CSV. Work with roles - Covers creating roles, assigning roles to users, and role management basics. Learning Experience: Role Based Access Control - Details standard roles and how they function in LXP. Learning Experience: Bulk add users to a Community (Group) - Describes bulk adding users to communities/groups. Directly adding users to communities without invitation acceptance - Explains the LD flag and 500-user bulk limit for community membership. How can I Upload or Update Users in Bulk? (Edge Import) - Introduces Edge Import for large-scale user creation and updates."</t>
   </si>
 </sst>
 </file>
@@ -436,49 +396,25 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>5</v>
-      </c>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
     </row>
-    <row r="3" spans="1:3" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>8</v>
-      </c>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
     </row>
-    <row r="4" spans="1:3" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>11</v>
-      </c>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
     </row>
-    <row r="5" spans="1:3" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>14</v>
-      </c>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/src/test/resources/input/AI_Test_Data.xlsx
+++ b/src/test/resources/input/AI_Test_Data.xlsx
@@ -3,14 +3,18 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14370" windowHeight="6135"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7650"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
-  <oleSize ref="A1"/>
 </workbook>
 </file>
 
